--- a/annual-config.xlsx
+++ b/annual-config.xlsx
@@ -161,6 +161,16 @@
           <t xml:space="preserve">1/9/2026</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/30/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -511,6 +521,16 @@
           <t xml:space="preserve">1/28/2026</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/30/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -599,6 +619,11 @@
           <t xml:space="preserve">5/5/2026</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/30/2026</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
@@ -1169,6 +1194,16 @@
           <t xml:space="preserve">1/28/2026</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/30/2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1186,6 +1221,16 @@
           <t xml:space="preserve">1/28/2026</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/30/2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1247,6 +1292,11 @@
           <t xml:space="preserve">5/5/2026</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/30/2026</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
@@ -1282,6 +1332,168 @@
       <c r="F67" t="inlineStr">
         <is>
           <t xml:space="preserve">Pavel Bittner</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olav Kooij</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daniel</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/30/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santiago Buitrago</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Richard Carapaz</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daniel</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/30/2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ethan Vernon</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Max Kanter</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daniel</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/30/2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lorenzo Fortunato</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Davide Piganzoli</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tanner</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/30/2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jan Christen</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mathias Vacek</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tanner</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/30/2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mauro Schmid</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soren Waerenskjold</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tanner</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/30/2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primoz Roglic</t>
         </is>
       </c>
     </row>

--- a/annual-config.xlsx
+++ b/annual-config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_1E6278B0C8C45D5F1061036690023C0E2103FDB0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB06C8CE-3D63-4AE3-BD27-9B297DD09DC4}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_1E6278B0C8C45D5F1061036690023C0E2103FDB0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE98C884-1258-475F-A744-A00B652B07A4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,9 +71,6 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>Wout Van Aert</t>
-  </si>
-  <si>
     <t>Matteo Jorgenson</t>
   </si>
   <si>
@@ -657,6 +654,9 @@
   </si>
   <si>
     <t>Mathieu van der Poel</t>
+  </si>
+  <si>
+    <t>Wout van Aert</t>
   </si>
 </sst>
 </file>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>211</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -1644,7 +1644,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
@@ -1655,7 +1655,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
@@ -1699,7 +1699,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -1732,7 +1732,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
@@ -1743,7 +1743,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
@@ -1765,7 +1765,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
         <v>7</v>
@@ -1776,7 +1776,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
         <v>7</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
@@ -1798,7 +1798,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s">
         <v>7</v>
@@ -1809,7 +1809,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
@@ -1820,16 +1820,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
         <v>33</v>
-      </c>
-      <c r="B26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" t="s">
-        <v>34</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -1837,24 +1837,24 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
         <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
@@ -1865,27 +1865,27 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -1893,16 +1893,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" t="s">
         <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -1910,13 +1910,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
@@ -1925,49 +1925,49 @@
         <v>15</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
         <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
       </c>
       <c r="F33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
         <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
       </c>
       <c r="F34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
@@ -1986,10 +1986,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" t="s">
         <v>8</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
         <v>8</v>
@@ -2008,10 +2008,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
         <v>8</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
         <v>8</v>
@@ -2030,10 +2030,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
         <v>8</v>
@@ -2041,16 +2041,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C42" t="s">
         <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C43" t="s">
         <v>8</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44" t="s">
         <v>8</v>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" t="s">
         <v>8</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C46" t="s">
         <v>8</v>
@@ -2102,16 +2102,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47" t="s">
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48" t="s">
         <v>8</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C50" t="s">
         <v>8</v>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C51" t="s">
         <v>8</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C52" t="s">
         <v>8</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C53" t="s">
         <v>8</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C54" t="s">
         <v>8</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C55" t="s">
         <v>8</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C56" t="s">
         <v>8</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C57" t="s">
         <v>8</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C58" t="s">
         <v>8</v>
@@ -2240,16 +2240,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -2257,35 +2257,35 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C62" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D62" t="s">
         <v>14</v>
@@ -2296,13 +2296,13 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B63" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C63" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D63" t="s">
         <v>14</v>
@@ -2313,41 +2313,41 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C64" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
       </c>
       <c r="F65" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B66" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D66" t="s">
         <v>14</v>
@@ -2356,32 +2356,32 @@
         <v>15</v>
       </c>
       <c r="F66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B67" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
       </c>
       <c r="F67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B68" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
@@ -2390,15 +2390,15 @@
         <v>15</v>
       </c>
       <c r="F68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
@@ -2407,15 +2407,15 @@
         <v>15</v>
       </c>
       <c r="F69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -2424,12 +2424,12 @@
         <v>15</v>
       </c>
       <c r="F70" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B71" t="s">
         <v>7</v>
@@ -2441,12 +2441,12 @@
         <v>15</v>
       </c>
       <c r="F71" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B72" t="s">
         <v>7</v>
@@ -2458,12 +2458,12 @@
         <v>15</v>
       </c>
       <c r="F72" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B73" t="s">
         <v>7</v>
@@ -2490,856 +2490,856 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
         <v>82</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>83</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>84</v>
-      </c>
-      <c r="D1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="s">
         <v>86</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>87</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
         <v>90</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
         <v>91</v>
-      </c>
-      <c r="C3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" t="s">
         <v>93</v>
       </c>
-      <c r="B4" t="s">
-        <v>94</v>
-      </c>
       <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="s">
         <v>88</v>
-      </c>
-      <c r="D4" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" t="s">
         <v>95</v>
       </c>
-      <c r="B5" t="s">
-        <v>96</v>
-      </c>
       <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
         <v>88</v>
-      </c>
-      <c r="D5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" t="s">
         <v>97</v>
       </c>
-      <c r="B6" t="s">
-        <v>98</v>
-      </c>
       <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" t="s">
         <v>88</v>
-      </c>
-      <c r="D6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
         <v>99</v>
       </c>
-      <c r="B7" t="s">
-        <v>100</v>
-      </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" t="s">
         <v>101</v>
       </c>
-      <c r="B8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" t="s">
-        <v>102</v>
-      </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" t="s">
         <v>103</v>
       </c>
-      <c r="B9" t="s">
-        <v>104</v>
-      </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" t="s">
         <v>106</v>
       </c>
-      <c r="B11" t="s">
-        <v>107</v>
-      </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" t="s">
         <v>108</v>
       </c>
-      <c r="B12" t="s">
-        <v>109</v>
-      </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" t="s">
         <v>110</v>
       </c>
-      <c r="B13" t="s">
-        <v>111</v>
-      </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" t="s">
         <v>112</v>
       </c>
-      <c r="B14" t="s">
-        <v>113</v>
-      </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" t="s">
         <v>115</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>116</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>117</v>
-      </c>
-      <c r="D16" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" t="s">
         <v>119</v>
       </c>
-      <c r="B17" t="s">
-        <v>120</v>
-      </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B18" t="s">
         <v>121</v>
       </c>
-      <c r="B18" t="s">
-        <v>122</v>
-      </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" t="s">
         <v>123</v>
       </c>
-      <c r="B19" t="s">
-        <v>124</v>
-      </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" t="s">
         <v>125</v>
       </c>
-      <c r="B20" t="s">
-        <v>126</v>
-      </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" t="s">
         <v>127</v>
       </c>
-      <c r="B21" t="s">
-        <v>128</v>
-      </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>128</v>
+      </c>
+      <c r="B22" t="s">
         <v>129</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>130</v>
       </c>
-      <c r="C22" t="s">
-        <v>131</v>
-      </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" t="s">
         <v>132</v>
       </c>
-      <c r="B23" t="s">
-        <v>133</v>
-      </c>
       <c r="C23" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" t="s">
         <v>117</v>
-      </c>
-      <c r="D23" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" t="s">
         <v>134</v>
       </c>
-      <c r="B24" t="s">
-        <v>135</v>
-      </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" t="s">
         <v>136</v>
       </c>
-      <c r="B25" t="s">
-        <v>137</v>
-      </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" t="s">
         <v>138</v>
       </c>
-      <c r="B26" t="s">
-        <v>139</v>
-      </c>
       <c r="C26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" t="s">
         <v>117</v>
-      </c>
-      <c r="D26" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" t="s">
         <v>140</v>
       </c>
-      <c r="B27" t="s">
-        <v>141</v>
-      </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" t="s">
         <v>142</v>
       </c>
-      <c r="B28" t="s">
-        <v>143</v>
-      </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" t="s">
         <v>144</v>
       </c>
-      <c r="B29" t="s">
-        <v>145</v>
-      </c>
       <c r="C29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" t="s">
         <v>88</v>
-      </c>
-      <c r="D29" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" t="s">
         <v>146</v>
       </c>
-      <c r="B30" t="s">
-        <v>147</v>
-      </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" t="s">
         <v>148</v>
       </c>
-      <c r="B31" t="s">
-        <v>149</v>
-      </c>
       <c r="C31" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" t="s">
         <v>117</v>
-      </c>
-      <c r="D31" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>149</v>
+      </c>
+      <c r="B32" t="s">
         <v>150</v>
       </c>
-      <c r="B32" t="s">
-        <v>151</v>
-      </c>
       <c r="C32" t="s">
+        <v>87</v>
+      </c>
+      <c r="D32" t="s">
         <v>88</v>
-      </c>
-      <c r="D32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" t="s">
         <v>152</v>
       </c>
-      <c r="B33" t="s">
-        <v>153</v>
-      </c>
       <c r="C33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>153</v>
+      </c>
+      <c r="B34" t="s">
         <v>154</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" t="s">
         <v>155</v>
-      </c>
-      <c r="C34" t="s">
-        <v>117</v>
-      </c>
-      <c r="D34" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" t="s">
         <v>157</v>
       </c>
-      <c r="B35" t="s">
-        <v>158</v>
-      </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" t="s">
         <v>159</v>
       </c>
-      <c r="B36" t="s">
-        <v>160</v>
-      </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" t="s">
         <v>161</v>
       </c>
-      <c r="B37" t="s">
-        <v>162</v>
-      </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" t="s">
         <v>163</v>
       </c>
-      <c r="B38" t="s">
-        <v>164</v>
-      </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>164</v>
+      </c>
+      <c r="B39" t="s">
         <v>165</v>
       </c>
-      <c r="B39" t="s">
-        <v>166</v>
-      </c>
       <c r="C39" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D39" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>166</v>
+      </c>
+      <c r="B40" t="s">
         <v>167</v>
       </c>
-      <c r="B40" t="s">
-        <v>168</v>
-      </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>168</v>
+      </c>
+      <c r="B41" t="s">
         <v>169</v>
       </c>
-      <c r="B41" t="s">
-        <v>170</v>
-      </c>
       <c r="C41" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" t="s">
         <v>88</v>
-      </c>
-      <c r="D41" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B42" t="s">
         <v>171</v>
       </c>
-      <c r="B42" t="s">
-        <v>172</v>
-      </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" t="s">
         <v>173</v>
       </c>
-      <c r="B43" t="s">
-        <v>174</v>
-      </c>
       <c r="C43" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" t="s">
         <v>88</v>
-      </c>
-      <c r="D43" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44" t="s">
         <v>175</v>
       </c>
-      <c r="B44" t="s">
-        <v>176</v>
-      </c>
       <c r="C44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D44" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>176</v>
+      </c>
+      <c r="B45" t="s">
         <v>177</v>
       </c>
-      <c r="B45" t="s">
-        <v>178</v>
-      </c>
       <c r="C45" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" t="s">
         <v>88</v>
-      </c>
-      <c r="D45" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>178</v>
+      </c>
+      <c r="B46" t="s">
         <v>179</v>
       </c>
-      <c r="B46" t="s">
-        <v>180</v>
-      </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>180</v>
+      </c>
+      <c r="B47" t="s">
         <v>181</v>
       </c>
-      <c r="B47" t="s">
-        <v>182</v>
-      </c>
       <c r="C47" t="s">
+        <v>87</v>
+      </c>
+      <c r="D47" t="s">
         <v>88</v>
-      </c>
-      <c r="D47" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" t="s">
         <v>183</v>
       </c>
-      <c r="B48" t="s">
-        <v>184</v>
-      </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>184</v>
+      </c>
+      <c r="B49" t="s">
         <v>185</v>
       </c>
-      <c r="B49" t="s">
-        <v>186</v>
-      </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>186</v>
+      </c>
+      <c r="B50" t="s">
         <v>187</v>
       </c>
-      <c r="B50" t="s">
-        <v>188</v>
-      </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>188</v>
+      </c>
+      <c r="B51" t="s">
         <v>189</v>
       </c>
-      <c r="B51" t="s">
-        <v>190</v>
-      </c>
       <c r="C51" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>190</v>
+      </c>
+      <c r="B52" t="s">
         <v>191</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
+        <v>116</v>
+      </c>
+      <c r="D52" t="s">
         <v>192</v>
-      </c>
-      <c r="C52" t="s">
-        <v>117</v>
-      </c>
-      <c r="D52" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" t="s">
         <v>194</v>
       </c>
-      <c r="B53" t="s">
-        <v>195</v>
-      </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>195</v>
+      </c>
+      <c r="B54" t="s">
         <v>196</v>
       </c>
-      <c r="B54" t="s">
-        <v>197</v>
-      </c>
       <c r="C54" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B55" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C55" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D55" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>198</v>
+      </c>
+      <c r="B56" t="s">
         <v>199</v>
       </c>
-      <c r="B56" t="s">
-        <v>200</v>
-      </c>
       <c r="C56" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D56" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>200</v>
+      </c>
+      <c r="B57" t="s">
         <v>201</v>
       </c>
-      <c r="B57" t="s">
-        <v>202</v>
-      </c>
       <c r="C57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>202</v>
+      </c>
+      <c r="B58" t="s">
         <v>203</v>
       </c>
-      <c r="B58" t="s">
-        <v>204</v>
-      </c>
       <c r="C58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>204</v>
+      </c>
+      <c r="B59" t="s">
         <v>205</v>
       </c>
-      <c r="B59" t="s">
-        <v>206</v>
-      </c>
       <c r="C59" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" t="s">
         <v>117</v>
-      </c>
-      <c r="D59" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>206</v>
+      </c>
+      <c r="B60" t="s">
         <v>207</v>
       </c>
-      <c r="B60" t="s">
-        <v>208</v>
-      </c>
       <c r="C60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D60" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>208</v>
+      </c>
+      <c r="B61" t="s">
         <v>209</v>
       </c>
-      <c r="B61" t="s">
-        <v>210</v>
-      </c>
       <c r="C61" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/annual-config.xlsx
+++ b/annual-config.xlsx
@@ -554,7 +554,7 @@
     <t>Renewi Tour</t>
   </si>
   <si>
-    <t>Aug 24 – Aug 30</t>
+    <t>Aug 19 – Aug 23</t>
   </si>
   <si>
     <t>Bretagne Classic - Ouest-France</t>

--- a/annual-config.xlsx
+++ b/annual-config.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
   <si>
     <t>rider_name</t>
   </si>
@@ -657,6 +657,24 @@
   </si>
   <si>
     <t>Wout van Aert</t>
+  </si>
+  <si>
+    <t>8/21/2026</t>
+  </si>
+  <si>
+    <t>Andreas Leknessund</t>
+  </si>
+  <si>
+    <t>Raul Garcia Pierna</t>
+  </si>
+  <si>
+    <t>Jorgen Nordhagen</t>
+  </si>
+  <si>
+    <t>Harold Tejada</t>
+  </si>
+  <si>
+    <t>Bryan Coquard</t>
   </si>
 </sst>
 </file>
@@ -1517,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
@@ -1674,6 +1692,9 @@
       <c r="C12" t="s">
         <v>8</v>
       </c>
+      <c r="D12" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1751,6 +1772,9 @@
       <c r="C19" t="s">
         <v>8</v>
       </c>
+      <c r="D19" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -2226,6 +2250,9 @@
       <c r="C57" t="s">
         <v>8</v>
       </c>
+      <c r="D57" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -2265,6 +2292,9 @@
       <c r="C60" t="s">
         <v>35</v>
       </c>
+      <c r="D60" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
@@ -2332,6 +2362,9 @@
       <c r="C65" t="s">
         <v>33</v>
       </c>
+      <c r="D65" t="s">
+        <v>212</v>
+      </c>
       <c r="E65" t="s">
         <v>15</v>
       </c>
@@ -2437,6 +2470,9 @@
       <c r="C71" t="s">
         <v>14</v>
       </c>
+      <c r="D71" t="s">
+        <v>212</v>
+      </c>
       <c r="E71" t="s">
         <v>15</v>
       </c>
@@ -2476,6 +2512,108 @@
       </c>
       <c r="F73" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>213</v>
+      </c>
+      <c r="B74" t="s">
+        <v>44</v>
+      </c>
+      <c r="C74" t="s">
+        <v>212</v>
+      </c>
+      <c r="E74" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>214</v>
+      </c>
+      <c r="B75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" t="s">
+        <v>212</v>
+      </c>
+      <c r="E75" t="s">
+        <v>15</v>
+      </c>
+      <c r="F75" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>215</v>
+      </c>
+      <c r="B76" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" t="s">
+        <v>212</v>
+      </c>
+      <c r="E76" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>71</v>
+      </c>
+      <c r="B77" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77" t="s">
+        <v>212</v>
+      </c>
+      <c r="E77" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>216</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" t="s">
+        <v>212</v>
+      </c>
+      <c r="E78" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>217</v>
+      </c>
+      <c r="B79" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" t="s">
+        <v>212</v>
+      </c>
+      <c r="E79" t="s">
+        <v>15</v>
+      </c>
+      <c r="F79" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
